--- a/admin/구매신청-김영섭.xlsx
+++ b/admin/구매신청-김영섭.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DSpy\admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21924" windowHeight="9084" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21924" windowHeight="9084" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="도서구입" sheetId="4" r:id="rId1"/>
     <sheet name="연구환경비" sheetId="2" r:id="rId2"/>
     <sheet name="재료비" sheetId="3" r:id="rId3"/>
+    <sheet name="문구류" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>퓨렐 손소독제 손세정제 30ml(휴대용)</t>
   </si>
@@ -73,6 +74,9 @@
   <si>
     <t>교보문고</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.staybooks.net/goods/goods_view.php?goodsNo=1000161972&amp;inflow=naver&amp;NaPm=ct%3Dkq28c4s0%7Cci%3D40ae5bb3ed8121f2676123ecce6ee7e83c05ddc6%7Ctr%3Daifcc%7Csn%3D426313%7Chk%3D0634ccbb0a96a642640005400611fb08690003f9</t>
   </si>
 </sst>
 </file>
@@ -436,6 +440,49 @@
         <a:xfrm>
           <a:off x="0" y="10981765"/>
           <a:ext cx="10272650" cy="4115157"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>351422</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>15835</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="662940"/>
+          <a:ext cx="10409822" cy="6866215"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -890,4 +937,21 @@
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>